--- a/content/blurb_worklist.xlsx
+++ b/content/blurb_worklist.xlsx
@@ -1840,7 +1840,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>TE8 or better every year as a starter</t>
+          <t>TE8 or better every year as a starter. 2026 update: still a real weekly floor, but production has stepped down from his peak -- treat our TE4 as more like a TE6-8 outcome.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
